--- a/public/results/2025/2025 Weekly Stats - Week 6.xlsx
+++ b/public/results/2025/2025 Weekly Stats - Week 6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mthutter/CODE/golf-league-site/public/results/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4714B3AD-2552-AF4A-B5A0-C8EDCE75B67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF34B3A3-5DA3-6146-B922-F1643D786C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4240" yWindow="2240" windowWidth="29860" windowHeight="16420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4240" yWindow="2240" windowWidth="29860" windowHeight="16420" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="14" r:id="rId1"/>

--- a/public/results/2025/2025 Weekly Stats - Week 6.xlsx
+++ b/public/results/2025/2025 Weekly Stats - Week 6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mthutter/CODE/golf-league-site/public/results/2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amentumcms-my.sharepoint.com/personal/mark_hutter_amentumcms_com/Documents/DATA/Code/golf-league-site/public/results/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF34B3A3-5DA3-6146-B922-F1643D786C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{AF34B3A3-5DA3-6146-B922-F1643D786C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDFB64AA-3A46-43E1-90D3-1C8D29CB3C3D}"/>
   <bookViews>
-    <workbookView xWindow="4240" yWindow="2240" windowWidth="29860" windowHeight="16420" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43695" yWindow="885" windowWidth="26730" windowHeight="18135" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="14" r:id="rId1"/>
@@ -342,7 +342,7 @@
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -557,7 +557,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -1167,45 +1167,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -1249,7 +1210,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1564,29 +1525,53 @@
     <xf numFmtId="1" fontId="23" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="8" fontId="24" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1595,6 +1580,72 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1619,72 +1670,6 @@
     <xf numFmtId="1" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1694,43 +1679,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="8" fontId="24" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="23" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2304,42 +2253,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75685173-5684-4D7E-8458-1B841D06EDCF}">
   <dimension ref="A1:Z21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23" style="3" customWidth="1"/>
     <col min="2" max="2" width="15" style="3" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.1640625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="7.5" style="3" customWidth="1"/>
-    <col min="15" max="15" width="17.1640625" style="3" customWidth="1"/>
-    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.6640625" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.6640625" style="33" customWidth="1"/>
-    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="3"/>
+    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="7.42578125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="17.140625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.7109375" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.7109375" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" style="33" customWidth="1"/>
+    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+    <row r="1" spans="1:26" ht="26.25">
+      <c r="A1" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
+      <c r="O1" s="135"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
@@ -2352,24 +2301,24 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A2" s="128" t="s">
+    <row r="2" spans="1:26">
+      <c r="A2" s="136" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="135"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -2382,7 +2331,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -2410,7 +2359,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75">
       <c r="A4" s="20" t="s">
         <v>16</v>
       </c>
@@ -2470,7 +2419,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>22</v>
@@ -2523,7 +2472,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>37</v>
@@ -2571,7 +2520,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75">
       <c r="A7" s="12"/>
       <c r="B7" s="13" t="s">
         <v>36</v>
@@ -2607,7 +2556,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>38</v>
@@ -2669,7 +2618,7 @@
       <c r="X8" s="2"/>
       <c r="Z8" s="36"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75">
       <c r="A9" s="12"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -2696,7 +2645,7 @@
       <c r="R9" s="31"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17" t="str">
@@ -2750,7 +2699,7 @@
       <c r="R10" s="31"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75">
       <c r="A11" s="12"/>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -2778,7 +2727,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17" t="str">
@@ -2833,7 +2782,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75">
       <c r="A13" s="12"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2861,7 +2810,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17" t="str">
@@ -2916,7 +2865,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75">
       <c r="A15" s="12"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2947,7 +2896,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17" t="str">
@@ -3005,7 +2954,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75">
       <c r="A17" s="12"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -3036,7 +2985,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17" t="str">
@@ -3094,7 +3043,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75">
       <c r="A19" s="12"/>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -3121,7 +3070,7 @@
       <c r="R19" s="31"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17" t="str">
@@ -3175,7 +3124,7 @@
       <c r="R20" s="31"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:26" ht="15" customHeight="1">
       <c r="E21" s="30"/>
       <c r="G21" s="30"/>
       <c r="H21" s="30"/>
@@ -3201,20 +3150,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E789909-84FC-488D-8D94-3FAD76B00BC6}">
   <dimension ref="A1:B1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" style="3" customWidth="1"/>
-    <col min="3" max="26" width="7.6640625" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="12.6640625" style="3"/>
+    <col min="1" max="1" width="20.28515625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" style="3" customWidth="1"/>
+    <col min="3" max="26" width="7.7109375" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="12.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" s="9" t="s">
         <v>30</v>
       </c>
@@ -3222,7 +3171,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" s="10">
         <v>-5</v>
       </c>
@@ -3230,7 +3179,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" s="10">
         <v>-4</v>
       </c>
@@ -3238,7 +3187,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" s="10">
         <v>-3</v>
       </c>
@@ -3246,7 +3195,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7" s="10">
         <v>-2</v>
       </c>
@@ -3254,7 +3203,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8" s="10">
         <v>-1</v>
       </c>
@@ -3262,7 +3211,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9" s="10">
         <v>0</v>
       </c>
@@ -3270,7 +3219,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10" s="10">
         <v>1</v>
       </c>
@@ -3278,7 +3227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11" s="10">
         <v>2</v>
       </c>
@@ -3286,7 +3235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12" s="10">
         <v>3</v>
       </c>
@@ -3294,7 +3243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13" s="10">
         <v>4</v>
       </c>
@@ -3302,7 +3251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14" s="10">
         <v>5</v>
       </c>
@@ -3310,7 +3259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15" s="10">
         <v>6</v>
       </c>
@@ -3318,996 +3267,996 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1">
       <c r="A17" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="14" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1" ht="14.25">
       <c r="A18" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="22" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="23" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="24" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="25" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="26" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="27" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="28" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="29" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="30" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="31" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="32" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="21" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="22" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="23" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="24" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:1" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A18" r:id="rId1" xr:uid="{BB8AB8C5-9F96-41D8-B252-ACC21DAB1BB3}"/>
@@ -4320,139 +4269,140 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A1EE897-404D-4ADC-856A-1E864FE4E3AA}">
   <dimension ref="A1:Z27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
-    <col min="4" max="9" width="7.83203125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="7.83203125" customWidth="1"/>
-    <col min="11" max="15" width="6.83203125" customWidth="1"/>
-    <col min="16" max="17" width="6.6640625" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="4" max="9" width="7.85546875" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" customWidth="1"/>
+    <col min="11" max="15" width="6.85546875" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="17" width="7.85546875" customWidth="1"/>
     <col min="18" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="5.6640625" customWidth="1"/>
-    <col min="20" max="20" width="6.33203125" customWidth="1"/>
-    <col min="21" max="21" width="10.83203125" customWidth="1"/>
-    <col min="22" max="22" width="8.5" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="6.83203125" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="8.5" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="10.6640625" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="6.5703125" customWidth="1"/>
+    <col min="20" max="20" width="6.28515625" customWidth="1"/>
+    <col min="21" max="21" width="10.85546875" customWidth="1"/>
+    <col min="22" max="22" width="8.42578125" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="6.85546875" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="8.42578125" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="1" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="129" t="s">
+    <row r="1" spans="1:26" s="1" customFormat="1" ht="24.95" customHeight="1" thickBot="1">
+      <c r="A1" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="135" t="s">
+      <c r="B1" s="160"/>
+      <c r="C1" s="165" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="137" t="s">
+      <c r="D1" s="139" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="138"/>
-      <c r="F1" s="137" t="s">
+      <c r="E1" s="140"/>
+      <c r="F1" s="139" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="138"/>
-      <c r="H1" s="137" t="s">
+      <c r="G1" s="140"/>
+      <c r="H1" s="139" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="138"/>
-      <c r="J1" s="137" t="s">
+      <c r="I1" s="140"/>
+      <c r="J1" s="139" t="s">
         <v>83</v>
       </c>
-      <c r="K1" s="138"/>
-      <c r="L1" s="137" t="s">
+      <c r="K1" s="140"/>
+      <c r="L1" s="139" t="s">
         <v>86</v>
       </c>
-      <c r="M1" s="138"/>
-      <c r="N1" s="137" t="s">
+      <c r="M1" s="140"/>
+      <c r="N1" s="139" t="s">
         <v>89</v>
       </c>
-      <c r="O1" s="138"/>
-      <c r="P1" s="146" t="s">
+      <c r="O1" s="140"/>
+      <c r="P1" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="148" t="s">
+      <c r="Q1" s="143" t="s">
         <v>45</v>
       </c>
-      <c r="R1" s="149"/>
-      <c r="S1" s="149"/>
-      <c r="T1" s="149"/>
-      <c r="U1" s="150"/>
-      <c r="V1" s="141" t="s">
+      <c r="R1" s="144"/>
+      <c r="S1" s="144"/>
+      <c r="T1" s="144"/>
+      <c r="U1" s="145"/>
+      <c r="V1" s="154" t="s">
         <v>46</v>
       </c>
-      <c r="W1" s="142"/>
-      <c r="X1" s="142"/>
-      <c r="Y1" s="142"/>
-      <c r="Z1" s="143"/>
-    </row>
-    <row r="2" spans="1:26" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="131"/>
-      <c r="B2" s="132"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="139">
+      <c r="W1" s="155"/>
+      <c r="X1" s="155"/>
+      <c r="Y1" s="155"/>
+      <c r="Z1" s="156"/>
+    </row>
+    <row r="2" spans="1:26" s="1" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A2" s="161"/>
+      <c r="B2" s="162"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="141">
         <v>45782</v>
       </c>
-      <c r="E2" s="140"/>
-      <c r="F2" s="139">
+      <c r="E2" s="142"/>
+      <c r="F2" s="141">
         <v>45789</v>
       </c>
-      <c r="G2" s="140"/>
-      <c r="H2" s="139">
+      <c r="G2" s="142"/>
+      <c r="H2" s="141">
         <v>45796</v>
       </c>
-      <c r="I2" s="140"/>
-      <c r="J2" s="139">
+      <c r="I2" s="142"/>
+      <c r="J2" s="141">
         <v>45803</v>
       </c>
-      <c r="K2" s="140"/>
-      <c r="L2" s="139">
+      <c r="K2" s="142"/>
+      <c r="L2" s="141">
         <v>45810</v>
       </c>
-      <c r="M2" s="140"/>
-      <c r="N2" s="139">
+      <c r="M2" s="142"/>
+      <c r="N2" s="141">
         <v>45817</v>
       </c>
-      <c r="O2" s="140"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="146" t="s">
+      <c r="O2" s="142"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="137" t="s">
         <v>41</v>
       </c>
-      <c r="R2" s="153" t="s">
+      <c r="R2" s="146" t="s">
         <v>44</v>
       </c>
-      <c r="S2" s="157" t="s">
+      <c r="S2" s="152" t="s">
         <v>78</v>
       </c>
-      <c r="T2" s="151" t="s">
+      <c r="T2" s="148" t="s">
         <v>13</v>
       </c>
-      <c r="U2" s="155" t="s">
+      <c r="U2" s="150" t="s">
         <v>33</v>
       </c>
-      <c r="V2" s="144" t="s">
+      <c r="V2" s="157" t="s">
         <v>41</v>
       </c>
-      <c r="W2" s="144" t="s">
+      <c r="W2" s="157" t="s">
         <v>44</v>
       </c>
-      <c r="X2" s="144" t="s">
+      <c r="X2" s="157" t="s">
         <v>78</v>
       </c>
-      <c r="Y2" s="144" t="s">
+      <c r="Y2" s="157" t="s">
         <v>13</v>
       </c>
-      <c r="Z2" s="144" t="s">
+      <c r="Z2" s="157" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="133"/>
-      <c r="B3" s="134"/>
-      <c r="C3" s="136"/>
+    <row r="3" spans="1:26" s="1" customFormat="1" ht="21.75" customHeight="1" thickBot="1">
+      <c r="A3" s="163"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="166"/>
       <c r="D3" s="38" t="s">
         <v>4</v>
       </c>
@@ -4489,19 +4439,19 @@
       <c r="O3" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="147"/>
-      <c r="Q3" s="147"/>
-      <c r="R3" s="154"/>
-      <c r="S3" s="158"/>
-      <c r="T3" s="152"/>
-      <c r="U3" s="156"/>
-      <c r="V3" s="145"/>
-      <c r="W3" s="145"/>
-      <c r="X3" s="145"/>
-      <c r="Y3" s="145"/>
-      <c r="Z3" s="145"/>
-    </row>
-    <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P3" s="138"/>
+      <c r="Q3" s="138"/>
+      <c r="R3" s="147"/>
+      <c r="S3" s="153"/>
+      <c r="T3" s="149"/>
+      <c r="U3" s="151"/>
+      <c r="V3" s="158"/>
+      <c r="W3" s="158"/>
+      <c r="X3" s="158"/>
+      <c r="Y3" s="158"/>
+      <c r="Z3" s="158"/>
+    </row>
+    <row r="4" spans="1:26" ht="15" customHeight="1">
       <c r="A4" s="39" t="s">
         <v>63</v>
       </c>
@@ -4511,20 +4461,20 @@
       <c r="C4" s="41">
         <v>22</v>
       </c>
-      <c r="D4" s="162" t="s">
+      <c r="D4" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="163"/>
+      <c r="E4" s="124"/>
       <c r="F4" s="67">
         <v>53</v>
       </c>
       <c r="G4" s="71">
         <v>23</v>
       </c>
-      <c r="H4" s="162" t="s">
+      <c r="H4" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="I4" s="163"/>
+      <c r="I4" s="124"/>
       <c r="J4" s="67"/>
       <c r="K4" s="71"/>
       <c r="L4" s="67"/>
@@ -4535,7 +4485,7 @@
       <c r="O4" s="71">
         <v>19</v>
       </c>
-      <c r="P4" s="118">
+      <c r="P4" s="55">
         <f>F4+J4+L4+N4</f>
         <v>110</v>
       </c>
@@ -4543,7 +4493,7 @@
         <f>COUNTIF(D4:N4,"&gt;30")</f>
         <v>2</v>
       </c>
-      <c r="R4" s="121"/>
+      <c r="R4" s="118"/>
       <c r="S4" s="71"/>
       <c r="T4" s="59">
         <f>SUMIF(G4:O4, "&lt;30")+R4+S4</f>
@@ -4561,7 +4511,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="15" customHeight="1">
       <c r="A5" s="42" t="s">
         <v>0</v>
       </c>
@@ -4571,16 +4521,16 @@
       <c r="C5" s="44">
         <v>15</v>
       </c>
-      <c r="D5" s="164"/>
-      <c r="E5" s="165"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="126"/>
       <c r="F5" s="45">
         <v>42</v>
       </c>
       <c r="G5" s="72">
         <v>27</v>
       </c>
-      <c r="H5" s="164"/>
-      <c r="I5" s="165"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="126"/>
       <c r="J5" s="45"/>
       <c r="K5" s="72"/>
       <c r="L5" s="45">
@@ -4591,7 +4541,7 @@
       </c>
       <c r="N5" s="45"/>
       <c r="O5" s="72"/>
-      <c r="P5" s="119">
+      <c r="P5" s="57">
         <f>F5+J5+L5+N5</f>
         <v>96</v>
       </c>
@@ -4599,7 +4549,7 @@
         <f>COUNTIF(D5:N5,"&gt;30")</f>
         <v>2</v>
       </c>
-      <c r="R5" s="122"/>
+      <c r="R5" s="119"/>
       <c r="S5" s="72"/>
       <c r="T5" s="60">
         <f>SUMIF(G5:O5, "&lt;30")+R5+S5</f>
@@ -4615,7 +4565,7 @@
       <c r="Y5" s="57"/>
       <c r="Z5" s="63"/>
     </row>
-    <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" ht="15" customHeight="1">
       <c r="A6" s="42" t="s">
         <v>52</v>
       </c>
@@ -4625,16 +4575,16 @@
       <c r="C6" s="44">
         <v>13</v>
       </c>
-      <c r="D6" s="164"/>
-      <c r="E6" s="165"/>
+      <c r="D6" s="125"/>
+      <c r="E6" s="126"/>
       <c r="F6" s="75">
         <v>42</v>
       </c>
       <c r="G6" s="72">
         <v>25</v>
       </c>
-      <c r="H6" s="164"/>
-      <c r="I6" s="165"/>
+      <c r="H6" s="125"/>
+      <c r="I6" s="126"/>
       <c r="J6" s="75"/>
       <c r="K6" s="72"/>
       <c r="L6" s="117">
@@ -4645,7 +4595,7 @@
       </c>
       <c r="N6" s="117"/>
       <c r="O6" s="72"/>
-      <c r="P6" s="119">
+      <c r="P6" s="57">
         <f>F6+J6+L6+N6</f>
         <v>93</v>
       </c>
@@ -4653,7 +4603,7 @@
         <f>COUNTIF(D6:N6,"&gt;30")</f>
         <v>2</v>
       </c>
-      <c r="R6" s="122">
+      <c r="R6" s="119">
         <v>1</v>
       </c>
       <c r="S6" s="72"/>
@@ -4671,7 +4621,7 @@
       <c r="Y6" s="57"/>
       <c r="Z6" s="63"/>
     </row>
-    <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="15" customHeight="1">
       <c r="A7" s="42" t="s">
         <v>52</v>
       </c>
@@ -4681,16 +4631,16 @@
       <c r="C7" s="44">
         <v>8</v>
       </c>
-      <c r="D7" s="164"/>
-      <c r="E7" s="165"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="126"/>
       <c r="F7" s="81">
         <v>45</v>
       </c>
       <c r="G7" s="72">
         <v>17</v>
       </c>
-      <c r="H7" s="164"/>
-      <c r="I7" s="165"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="126"/>
       <c r="J7" s="81"/>
       <c r="K7" s="72"/>
       <c r="L7" s="81">
@@ -4699,13 +4649,13 @@
       <c r="M7" s="72">
         <v>19</v>
       </c>
-      <c r="N7" s="173">
+      <c r="N7" s="132">
         <v>41</v>
       </c>
       <c r="O7" s="72">
         <v>21</v>
       </c>
-      <c r="P7" s="119">
+      <c r="P7" s="57">
         <f>F7+J7+L7+N7</f>
         <v>129</v>
       </c>
@@ -4713,7 +4663,7 @@
         <f>COUNTIF(D7:N7,"&gt;30")</f>
         <v>3</v>
       </c>
-      <c r="R7" s="122">
+      <c r="R7" s="119">
         <v>1</v>
       </c>
       <c r="S7" s="72">
@@ -4733,7 +4683,7 @@
       <c r="Y7" s="57"/>
       <c r="Z7" s="63"/>
     </row>
-    <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" ht="15" customHeight="1">
       <c r="A8" s="42" t="s">
         <v>61</v>
       </c>
@@ -4743,12 +4693,12 @@
       <c r="C8" s="44">
         <v>15</v>
       </c>
-      <c r="D8" s="164"/>
-      <c r="E8" s="165"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="126"/>
       <c r="F8" s="45"/>
       <c r="G8" s="72"/>
-      <c r="H8" s="164"/>
-      <c r="I8" s="165"/>
+      <c r="H8" s="125"/>
+      <c r="I8" s="126"/>
       <c r="J8" s="45">
         <v>52</v>
       </c>
@@ -4763,7 +4713,7 @@
       <c r="O8" s="72">
         <v>23</v>
       </c>
-      <c r="P8" s="119">
+      <c r="P8" s="57">
         <f>F8+J8+L8+N8</f>
         <v>98</v>
       </c>
@@ -4771,7 +4721,7 @@
         <f>COUNTIF(D8:N8,"&gt;30")</f>
         <v>2</v>
       </c>
-      <c r="R8" s="122"/>
+      <c r="R8" s="119"/>
       <c r="S8" s="72"/>
       <c r="T8" s="60">
         <f>SUMIF(G8:O8, "&lt;30")+R8+S8</f>
@@ -4781,13 +4731,13 @@
         <f>T8/Q8</f>
         <v>20</v>
       </c>
-      <c r="V8" s="171"/>
+      <c r="V8" s="130"/>
       <c r="W8" s="60"/>
       <c r="X8" s="60"/>
       <c r="Y8" s="57"/>
       <c r="Z8" s="63"/>
     </row>
-    <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="15" customHeight="1">
       <c r="A9" s="42" t="s">
         <v>2</v>
       </c>
@@ -4797,16 +4747,16 @@
       <c r="C9" s="44">
         <v>8</v>
       </c>
-      <c r="D9" s="164"/>
-      <c r="E9" s="165"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="126"/>
       <c r="F9" s="45">
         <v>46</v>
       </c>
       <c r="G9" s="72">
         <v>16</v>
       </c>
-      <c r="H9" s="164"/>
-      <c r="I9" s="165"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="126"/>
       <c r="J9" s="45"/>
       <c r="K9" s="72"/>
       <c r="L9" s="45"/>
@@ -4817,7 +4767,7 @@
       <c r="O9" s="72">
         <v>20</v>
       </c>
-      <c r="P9" s="119">
+      <c r="P9" s="57">
         <f>F9+J9+L9+N9</f>
         <v>88</v>
       </c>
@@ -4825,7 +4775,7 @@
         <f>COUNTIF(D9:N9,"&gt;30")</f>
         <v>2</v>
       </c>
-      <c r="R9" s="122"/>
+      <c r="R9" s="119"/>
       <c r="S9" s="72">
         <v>1</v>
       </c>
@@ -4843,7 +4793,7 @@
       <c r="Y9" s="57"/>
       <c r="Z9" s="63"/>
     </row>
-    <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" ht="15" customHeight="1">
       <c r="A10" s="42" t="s">
         <v>73</v>
       </c>
@@ -4853,16 +4803,16 @@
       <c r="C10" s="44">
         <v>10</v>
       </c>
-      <c r="D10" s="164"/>
-      <c r="E10" s="165"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="126"/>
       <c r="F10" s="45">
         <v>46</v>
       </c>
       <c r="G10" s="72">
         <v>18</v>
       </c>
-      <c r="H10" s="164"/>
-      <c r="I10" s="165"/>
+      <c r="H10" s="125"/>
+      <c r="I10" s="126"/>
       <c r="J10" s="45"/>
       <c r="K10" s="72"/>
       <c r="L10" s="45">
@@ -4877,7 +4827,7 @@
       <c r="O10" s="72">
         <v>18</v>
       </c>
-      <c r="P10" s="119">
+      <c r="P10" s="57">
         <f>F10+J10+L10+N10</f>
         <v>138</v>
       </c>
@@ -4885,7 +4835,7 @@
         <f>COUNTIF(D10:N10,"&gt;30")</f>
         <v>3</v>
       </c>
-      <c r="R10" s="123"/>
+      <c r="R10" s="120"/>
       <c r="S10" s="82"/>
       <c r="T10" s="60">
         <f>SUMIF(G10:O10, "&lt;30")+R10+S10</f>
@@ -4895,13 +4845,13 @@
         <f>T10/Q10</f>
         <v>18</v>
       </c>
-      <c r="V10" s="172"/>
+      <c r="V10" s="131"/>
       <c r="W10" s="57"/>
       <c r="X10" s="57"/>
       <c r="Y10" s="57"/>
       <c r="Z10" s="63"/>
     </row>
-    <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="15" customHeight="1">
       <c r="A11" s="42" t="s">
         <v>50</v>
       </c>
@@ -4911,16 +4861,16 @@
       <c r="C11" s="44">
         <v>21</v>
       </c>
-      <c r="D11" s="164"/>
-      <c r="E11" s="165"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="126"/>
       <c r="F11" s="79">
         <v>61</v>
       </c>
       <c r="G11" s="72">
         <v>14</v>
       </c>
-      <c r="H11" s="164"/>
-      <c r="I11" s="165"/>
+      <c r="H11" s="125"/>
+      <c r="I11" s="126"/>
       <c r="J11" s="79">
         <v>56</v>
       </c>
@@ -4939,7 +4889,7 @@
       <c r="O11" s="72">
         <v>19</v>
       </c>
-      <c r="P11" s="119">
+      <c r="P11" s="57">
         <f>F11+J11+L11+N11</f>
         <v>233</v>
       </c>
@@ -4947,7 +4897,7 @@
         <f>COUNTIF(D11:N11,"&gt;30")</f>
         <v>4</v>
       </c>
-      <c r="R11" s="122">
+      <c r="R11" s="119">
         <v>2</v>
       </c>
       <c r="S11" s="72"/>
@@ -4965,7 +4915,7 @@
       <c r="Y11" s="57"/>
       <c r="Z11" s="63"/>
     </row>
-    <row r="12" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" ht="15" customHeight="1">
       <c r="A12" s="42" t="s">
         <v>67</v>
       </c>
@@ -4975,23 +4925,23 @@
       <c r="C12" s="44">
         <v>22</v>
       </c>
-      <c r="D12" s="164"/>
-      <c r="E12" s="165"/>
+      <c r="D12" s="125"/>
+      <c r="E12" s="126"/>
       <c r="F12" s="45">
         <v>59</v>
       </c>
       <c r="G12" s="72">
         <v>17</v>
       </c>
-      <c r="H12" s="164"/>
-      <c r="I12" s="165"/>
+      <c r="H12" s="125"/>
+      <c r="I12" s="126"/>
       <c r="J12" s="45"/>
       <c r="K12" s="72"/>
       <c r="L12" s="45"/>
       <c r="M12" s="72"/>
       <c r="N12" s="45"/>
       <c r="O12" s="72"/>
-      <c r="P12" s="119">
+      <c r="P12" s="57">
         <f>F12+J12+L12+N12</f>
         <v>59</v>
       </c>
@@ -4999,7 +4949,7 @@
         <f>COUNTIF(D12:N12,"&gt;30")</f>
         <v>1</v>
       </c>
-      <c r="R12" s="122"/>
+      <c r="R12" s="119"/>
       <c r="S12" s="72"/>
       <c r="T12" s="60">
         <f>SUMIF(G12:O12, "&lt;30")+R12+S12</f>
@@ -5015,7 +4965,7 @@
       <c r="Y12" s="57"/>
       <c r="Z12" s="63"/>
     </row>
-    <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="15" customHeight="1">
       <c r="A13" s="42" t="s">
         <v>69</v>
       </c>
@@ -5025,23 +4975,23 @@
       <c r="C13" s="44">
         <v>18</v>
       </c>
-      <c r="D13" s="164"/>
-      <c r="E13" s="165"/>
+      <c r="D13" s="125"/>
+      <c r="E13" s="126"/>
       <c r="F13" s="45">
         <v>56</v>
       </c>
       <c r="G13" s="72">
         <v>16</v>
       </c>
-      <c r="H13" s="164"/>
-      <c r="I13" s="165"/>
+      <c r="H13" s="125"/>
+      <c r="I13" s="126"/>
       <c r="J13" s="45"/>
       <c r="K13" s="72"/>
       <c r="L13" s="45"/>
       <c r="M13" s="72"/>
       <c r="N13" s="45"/>
       <c r="O13" s="72"/>
-      <c r="P13" s="119">
+      <c r="P13" s="57">
         <f>F13+J13+L13+N13</f>
         <v>56</v>
       </c>
@@ -5049,7 +4999,7 @@
         <f>COUNTIF(D13:N13,"&gt;30")</f>
         <v>1</v>
       </c>
-      <c r="R13" s="122"/>
+      <c r="R13" s="119"/>
       <c r="S13" s="72"/>
       <c r="T13" s="60">
         <f>SUMIF(G13:O13, "&lt;30")+R13+S13</f>
@@ -5065,7 +5015,7 @@
       <c r="Y13" s="57"/>
       <c r="Z13" s="63"/>
     </row>
-    <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" ht="15" customHeight="1">
       <c r="A14" s="42" t="s">
         <v>3</v>
       </c>
@@ -5075,16 +5025,16 @@
       <c r="C14" s="44">
         <v>17</v>
       </c>
-      <c r="D14" s="164"/>
-      <c r="E14" s="165"/>
+      <c r="D14" s="125"/>
+      <c r="E14" s="126"/>
       <c r="F14" s="45">
         <v>55</v>
       </c>
       <c r="G14" s="72">
         <v>16</v>
       </c>
-      <c r="H14" s="164"/>
-      <c r="I14" s="165"/>
+      <c r="H14" s="125"/>
+      <c r="I14" s="126"/>
       <c r="J14" s="45"/>
       <c r="K14" s="72"/>
       <c r="L14" s="45">
@@ -5099,7 +5049,7 @@
       <c r="O14" s="72">
         <v>14</v>
       </c>
-      <c r="P14" s="119">
+      <c r="P14" s="57">
         <f>F14+J14+L14+N14</f>
         <v>168</v>
       </c>
@@ -5107,7 +5057,7 @@
         <f>COUNTIF(D14:N14,"&gt;30")</f>
         <v>3</v>
       </c>
-      <c r="R14" s="122"/>
+      <c r="R14" s="119"/>
       <c r="S14" s="72"/>
       <c r="T14" s="60">
         <f>SUMIF(G14:O14, "&lt;30")+R14+S14</f>
@@ -5123,7 +5073,7 @@
       <c r="Y14" s="57"/>
       <c r="Z14" s="63"/>
     </row>
-    <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="15" customHeight="1">
       <c r="A15" s="42" t="s">
         <v>71</v>
       </c>
@@ -5133,23 +5083,23 @@
       <c r="C15" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="164"/>
-      <c r="E15" s="165"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="126"/>
       <c r="F15" s="45">
         <v>41</v>
       </c>
       <c r="G15" s="72"/>
-      <c r="H15" s="164"/>
-      <c r="I15" s="165"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="126"/>
       <c r="J15" s="45"/>
       <c r="K15" s="72"/>
       <c r="L15" s="45"/>
       <c r="M15" s="72"/>
-      <c r="N15" s="174">
+      <c r="N15" s="133">
         <v>48</v>
       </c>
       <c r="O15" s="72"/>
-      <c r="P15" s="119">
+      <c r="P15" s="57">
         <f>F15+J15+L15+N15</f>
         <v>89</v>
       </c>
@@ -5157,7 +5107,7 @@
         <f>COUNTIF(D15:N15,"&gt;30")</f>
         <v>2</v>
       </c>
-      <c r="R15" s="122">
+      <c r="R15" s="119">
         <v>1</v>
       </c>
       <c r="S15" s="72"/>
@@ -5172,7 +5122,7 @@
       <c r="Y15" s="57"/>
       <c r="Z15" s="63"/>
     </row>
-    <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" ht="15" customHeight="1">
       <c r="A16" s="42" t="s">
         <v>87</v>
       </c>
@@ -5182,21 +5132,21 @@
       <c r="C16" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="164"/>
-      <c r="E16" s="165"/>
+      <c r="D16" s="125"/>
+      <c r="E16" s="126"/>
       <c r="F16" s="66"/>
       <c r="G16" s="72"/>
-      <c r="H16" s="164"/>
-      <c r="I16" s="165"/>
+      <c r="H16" s="125"/>
+      <c r="I16" s="126"/>
       <c r="J16" s="66"/>
       <c r="K16" s="72"/>
-      <c r="L16" s="125">
+      <c r="L16" s="122">
         <v>50</v>
       </c>
       <c r="M16" s="72"/>
-      <c r="N16" s="125"/>
+      <c r="N16" s="122"/>
       <c r="O16" s="72"/>
-      <c r="P16" s="119">
+      <c r="P16" s="57">
         <f>F16+J16+L16+N16</f>
         <v>50</v>
       </c>
@@ -5204,7 +5154,7 @@
         <f>COUNTIF(D16:N16,"&gt;30")</f>
         <v>1</v>
       </c>
-      <c r="R16" s="122">
+      <c r="R16" s="119">
         <v>1</v>
       </c>
       <c r="S16" s="72"/>
@@ -5219,7 +5169,7 @@
       <c r="Y16" s="57"/>
       <c r="Z16" s="63"/>
     </row>
-    <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="15" customHeight="1">
       <c r="A17" s="42" t="s">
         <v>57</v>
       </c>
@@ -5229,14 +5179,14 @@
       <c r="C17" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="164"/>
-      <c r="E17" s="165"/>
+      <c r="D17" s="125"/>
+      <c r="E17" s="126"/>
       <c r="F17" s="45">
         <v>51</v>
       </c>
       <c r="G17" s="72"/>
-      <c r="H17" s="164"/>
-      <c r="I17" s="165"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="126"/>
       <c r="J17" s="45"/>
       <c r="K17" s="72"/>
       <c r="L17" s="45"/>
@@ -5245,7 +5195,7 @@
         <v>51</v>
       </c>
       <c r="O17" s="72"/>
-      <c r="P17" s="119">
+      <c r="P17" s="57">
         <f>F17+J17+L17+N17</f>
         <v>102</v>
       </c>
@@ -5253,7 +5203,7 @@
         <f>COUNTIF(D17:N17,"&gt;30")</f>
         <v>2</v>
       </c>
-      <c r="R17" s="122"/>
+      <c r="R17" s="119"/>
       <c r="S17" s="72"/>
       <c r="T17" s="60">
         <f>SUMIF(G17:O17, "&lt;30")+R17+S17</f>
@@ -5266,40 +5216,41 @@
       <c r="Y17" s="57"/>
       <c r="Z17" s="63"/>
     </row>
-    <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:26" ht="15" customHeight="1">
       <c r="A18" s="42" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" s="44">
-        <v>13</v>
-      </c>
-      <c r="D18" s="164"/>
-      <c r="E18" s="165"/>
+        <v>93</v>
+      </c>
+      <c r="C18" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="125"/>
+      <c r="E18" s="126"/>
       <c r="F18" s="46"/>
       <c r="G18" s="72"/>
-      <c r="H18" s="164"/>
-      <c r="I18" s="165"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="126"/>
       <c r="J18" s="46"/>
       <c r="K18" s="72"/>
       <c r="L18" s="46"/>
       <c r="M18" s="72"/>
-      <c r="N18" s="46"/>
+      <c r="N18" s="117">
+        <v>45</v>
+      </c>
       <c r="O18" s="72"/>
-      <c r="P18" s="119">
+      <c r="P18" s="57">
         <f>F18+J18+L18+N18</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Q18" s="57">
         <f>COUNTIF(D18:N18,"&gt;30")</f>
-        <v>0</v>
-      </c>
-      <c r="R18" s="122"/>
+        <v>1</v>
+      </c>
+      <c r="R18" s="119"/>
       <c r="S18" s="72"/>
       <c r="T18" s="60">
-        <f>SUMIF(G18:O18, "&lt;30")+R18+S18</f>
         <v>0</v>
       </c>
       <c r="U18" s="84"/>
@@ -5309,29 +5260,29 @@
       <c r="Y18" s="57"/>
       <c r="Z18" s="63"/>
     </row>
-    <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="15" customHeight="1">
       <c r="A19" s="42" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C19" s="44">
-        <v>2</v>
-      </c>
-      <c r="D19" s="164"/>
-      <c r="E19" s="165"/>
-      <c r="F19" s="66"/>
+        <v>13</v>
+      </c>
+      <c r="D19" s="125"/>
+      <c r="E19" s="126"/>
+      <c r="F19" s="46"/>
       <c r="G19" s="72"/>
-      <c r="H19" s="164"/>
-      <c r="I19" s="165"/>
-      <c r="J19" s="66"/>
+      <c r="H19" s="125"/>
+      <c r="I19" s="126"/>
+      <c r="J19" s="46"/>
       <c r="K19" s="72"/>
-      <c r="L19" s="66"/>
+      <c r="L19" s="46"/>
       <c r="M19" s="72"/>
-      <c r="N19" s="66"/>
+      <c r="N19" s="46"/>
       <c r="O19" s="72"/>
-      <c r="P19" s="119">
+      <c r="P19" s="57">
         <f>F19+J19+L19+N19</f>
         <v>0</v>
       </c>
@@ -5339,7 +5290,7 @@
         <f>COUNTIF(D19:N19,"&gt;30")</f>
         <v>0</v>
       </c>
-      <c r="R19" s="122"/>
+      <c r="R19" s="119"/>
       <c r="S19" s="72"/>
       <c r="T19" s="60">
         <f>SUMIF(G19:O19, "&lt;30")+R19+S19</f>
@@ -5352,29 +5303,29 @@
       <c r="Y19" s="57"/>
       <c r="Z19" s="63"/>
     </row>
-    <row r="20" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:26" ht="15" customHeight="1">
       <c r="A20" s="42" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C20" s="44">
-        <v>15</v>
-      </c>
-      <c r="D20" s="164"/>
-      <c r="E20" s="165"/>
-      <c r="F20" s="45"/>
+        <v>2</v>
+      </c>
+      <c r="D20" s="125"/>
+      <c r="E20" s="126"/>
+      <c r="F20" s="66"/>
       <c r="G20" s="72"/>
-      <c r="H20" s="164"/>
-      <c r="I20" s="165"/>
-      <c r="J20" s="45"/>
+      <c r="H20" s="125"/>
+      <c r="I20" s="126"/>
+      <c r="J20" s="66"/>
       <c r="K20" s="72"/>
-      <c r="L20" s="45"/>
+      <c r="L20" s="66"/>
       <c r="M20" s="72"/>
-      <c r="N20" s="45"/>
+      <c r="N20" s="66"/>
       <c r="O20" s="72"/>
-      <c r="P20" s="119">
+      <c r="P20" s="57">
         <f>F20+J20+L20+N20</f>
         <v>0</v>
       </c>
@@ -5382,42 +5333,42 @@
         <f>COUNTIF(D20:N20,"&gt;30")</f>
         <v>0</v>
       </c>
-      <c r="R20" s="122"/>
+      <c r="R20" s="119"/>
       <c r="S20" s="72"/>
       <c r="T20" s="60">
         <f>SUMIF(G20:O20, "&lt;30")+R20+S20</f>
         <v>0</v>
       </c>
       <c r="U20" s="84"/>
-      <c r="V20" s="78"/>
+      <c r="V20" s="77"/>
       <c r="W20" s="60"/>
       <c r="X20" s="60"/>
       <c r="Y20" s="57"/>
       <c r="Z20" s="63"/>
     </row>
-    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="15" customHeight="1">
       <c r="A21" s="42" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C21" s="44">
-        <v>11</v>
-      </c>
-      <c r="D21" s="164"/>
-      <c r="E21" s="165"/>
+        <v>15</v>
+      </c>
+      <c r="D21" s="125"/>
+      <c r="E21" s="126"/>
       <c r="F21" s="45"/>
       <c r="G21" s="72"/>
-      <c r="H21" s="164"/>
-      <c r="I21" s="165"/>
+      <c r="H21" s="125"/>
+      <c r="I21" s="126"/>
       <c r="J21" s="45"/>
       <c r="K21" s="72"/>
       <c r="L21" s="45"/>
       <c r="M21" s="72"/>
       <c r="N21" s="45"/>
       <c r="O21" s="72"/>
-      <c r="P21" s="119">
+      <c r="P21" s="57">
         <f>F21+J21+L21+N21</f>
         <v>0</v>
       </c>
@@ -5425,48 +5376,55 @@
         <f>COUNTIF(D21:N21,"&gt;30")</f>
         <v>0</v>
       </c>
-      <c r="R21" s="122"/>
+      <c r="R21" s="119"/>
       <c r="S21" s="72"/>
       <c r="T21" s="60">
         <f>SUMIF(G21:O21, "&lt;30")+R21+S21</f>
         <v>0</v>
       </c>
       <c r="U21" s="84"/>
-      <c r="V21" s="77"/>
+      <c r="V21" s="78"/>
       <c r="W21" s="60"/>
       <c r="X21" s="60"/>
       <c r="Y21" s="57"/>
       <c r="Z21" s="63"/>
     </row>
-    <row r="22" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A22" s="68" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="B22" s="69" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="70" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="166"/>
-      <c r="E22" s="167"/>
-      <c r="F22" s="169"/>
+        <v>58</v>
+      </c>
+      <c r="C22" s="70">
+        <v>11</v>
+      </c>
+      <c r="D22" s="127"/>
+      <c r="E22" s="128"/>
+      <c r="F22" s="170"/>
       <c r="G22" s="73"/>
-      <c r="H22" s="166"/>
-      <c r="I22" s="167"/>
-      <c r="J22" s="169"/>
+      <c r="H22" s="127"/>
+      <c r="I22" s="128"/>
+      <c r="J22" s="170"/>
       <c r="K22" s="73"/>
-      <c r="L22" s="169"/>
+      <c r="L22" s="170"/>
       <c r="M22" s="73"/>
-      <c r="N22" s="170">
-        <v>45</v>
-      </c>
+      <c r="N22" s="170"/>
       <c r="O22" s="73"/>
-      <c r="P22" s="120"/>
-      <c r="Q22" s="58"/>
-      <c r="R22" s="124"/>
+      <c r="P22" s="58">
+        <f>F22+J22+L22+N22</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="58">
+        <f>COUNTIF(D22:N22,"&gt;30")</f>
+        <v>0</v>
+      </c>
+      <c r="R22" s="121"/>
       <c r="S22" s="73"/>
-      <c r="T22" s="61"/>
+      <c r="T22" s="61">
+        <f>SUMIF(G22:O22, "&lt;30")+R22+S22</f>
+        <v>0</v>
+      </c>
       <c r="U22" s="85"/>
       <c r="V22" s="80"/>
       <c r="W22" s="61"/>
@@ -5474,7 +5432,7 @@
       <c r="Y22" s="58"/>
       <c r="Z22" s="64"/>
     </row>
-    <row r="23" spans="1:26" s="51" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" s="51" customFormat="1" ht="15.75" thickBot="1">
       <c r="A23" s="86"/>
       <c r="B23" s="87"/>
       <c r="C23" s="87"/>
@@ -5504,7 +5462,7 @@
       <c r="O23" s="88"/>
       <c r="P23" s="89"/>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:26">
       <c r="C24" s="48"/>
       <c r="P24" s="49"/>
       <c r="Q24" s="49"/>
@@ -5513,7 +5471,7 @@
       <c r="T24" s="49"/>
       <c r="U24" s="50"/>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26">
       <c r="C25" s="90" t="s">
         <v>6</v>
       </c>
@@ -5526,7 +5484,7 @@
       <c r="L25" s="53"/>
       <c r="N25" s="53"/>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:26">
       <c r="C26" s="91" t="s">
         <v>7</v>
       </c>
@@ -5540,7 +5498,7 @@
       <c r="N26" s="52"/>
       <c r="P26" s="65"/>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26">
       <c r="C27" s="92" t="s">
         <v>84</v>
       </c>
@@ -5567,6 +5525,22 @@
     <sortCondition ref="B4:B22"/>
   </sortState>
   <mergeCells count="27">
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="V1:Z1"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="P1:P3"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="L2:M2"/>
@@ -5578,22 +5552,6 @@
     <mergeCell ref="S2:S3"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="V1:Z1"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="A1:B3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5607,37 +5565,37 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC552F5-687A-B14F-ACE0-F13F8118F4F8}">
   <dimension ref="A1:Z30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="3"/>
+    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="8.7109375" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+    <row r="1" spans="1:26" ht="26.25">
+      <c r="A1" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
+      <c r="O1" s="135"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
@@ -5650,24 +5608,24 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="128" t="s">
+    <row r="2" spans="1:26" ht="15">
+      <c r="A2" s="136" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="135"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -5680,7 +5638,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -5708,7 +5666,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75">
       <c r="A4" s="20" t="s">
         <v>16</v>
       </c>
@@ -5766,7 +5724,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>22</v>
@@ -5817,7 +5775,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>37</v>
@@ -5865,7 +5823,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75">
       <c r="A7" s="12"/>
       <c r="B7" s="13" t="s">
         <v>36</v>
@@ -5895,7 +5853,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>38</v>
@@ -5925,7 +5883,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75">
       <c r="A9" s="12"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -5953,7 +5911,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -5981,7 +5939,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75">
       <c r="A11" s="12"/>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6009,7 +5967,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -6037,7 +5995,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75">
       <c r="A13" s="12"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -6065,7 +6023,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -6093,7 +6051,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75">
       <c r="A15" s="12"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -6121,7 +6079,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -6149,7 +6107,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75">
       <c r="A17" s="12"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -6177,7 +6135,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -6205,7 +6163,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75">
       <c r="A19" s="12"/>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6233,7 +6191,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -6261,7 +6219,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75">
       <c r="A21" s="12"/>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -6289,7 +6247,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -6317,7 +6275,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75">
       <c r="A23" s="12"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -6345,7 +6303,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -6373,7 +6331,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="18.75">
       <c r="A25" s="12"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -6401,7 +6359,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" thickBot="1">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -6429,7 +6387,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="18.75">
       <c r="A27" s="12"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -6457,7 +6415,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="19.5" thickBot="1">
       <c r="A28" s="16"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -6485,7 +6443,7 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" ht="18.75">
       <c r="A29" s="12"/>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -6513,7 +6471,7 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="19.5" thickBot="1">
       <c r="A30" s="16"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -6557,37 +6515,37 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BEDCE9-6DB6-684C-9A36-B24C0B788429}">
   <dimension ref="A1:Z30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="3"/>
+    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="8.7109375" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+    <row r="1" spans="1:26" ht="26.25">
+      <c r="A1" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
+      <c r="O1" s="135"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
@@ -6600,24 +6558,24 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="128" t="s">
+    <row r="2" spans="1:26" ht="15">
+      <c r="A2" s="136" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="135"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -6630,7 +6588,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -6658,7 +6616,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75">
       <c r="A4" s="20" t="s">
         <v>16</v>
       </c>
@@ -6716,7 +6674,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>22</v>
@@ -6767,7 +6725,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>37</v>
@@ -6815,7 +6773,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75">
       <c r="A7" s="12" t="s">
         <v>26</v>
       </c>
@@ -6873,7 +6831,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>38</v>
@@ -6936,7 +6894,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75">
       <c r="A9" s="12" t="s">
         <v>27</v>
       </c>
@@ -6992,7 +6950,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -7053,7 +7011,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75">
       <c r="A11" s="12" t="s">
         <v>47</v>
       </c>
@@ -7106,7 +7064,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -7140,7 +7098,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75">
       <c r="A13" s="12" t="s">
         <v>23</v>
       </c>
@@ -7196,7 +7154,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -7257,7 +7215,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75">
       <c r="A15" s="12" t="s">
         <v>25</v>
       </c>
@@ -7313,7 +7271,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -7374,7 +7332,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75">
       <c r="A17" s="12" t="s">
         <v>43</v>
       </c>
@@ -7430,7 +7388,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -7491,7 +7449,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75">
       <c r="A19" s="12" t="s">
         <v>28</v>
       </c>
@@ -7547,7 +7505,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -7608,7 +7566,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75">
       <c r="A21" s="12" t="s">
         <v>34</v>
       </c>
@@ -7664,7 +7622,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17">
@@ -7725,7 +7683,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75">
       <c r="A23" s="12" t="s">
         <v>35</v>
       </c>
@@ -7781,7 +7739,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17">
@@ -7842,7 +7800,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="18.75">
       <c r="A25" s="12" t="s">
         <v>76</v>
       </c>
@@ -7895,7 +7853,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" thickBot="1">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17">
@@ -7956,7 +7914,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="18.75">
       <c r="A27" s="12" t="s">
         <v>77</v>
       </c>
@@ -8009,7 +7967,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="19.5" thickBot="1">
       <c r="A28" s="16"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -8040,7 +7998,7 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" ht="18.75">
       <c r="A29" s="12" t="s">
         <v>24</v>
       </c>
@@ -8096,7 +8054,7 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="19.5" thickBot="1">
       <c r="A30" s="16"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17">
@@ -8173,37 +8131,37 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{098E9CBB-8515-E247-BAE9-1E112AF74A33}">
   <dimension ref="A1:Z30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="3"/>
+    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="8.7109375" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+    <row r="1" spans="1:26" ht="26.25">
+      <c r="A1" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
+      <c r="O1" s="135"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
@@ -8216,24 +8174,24 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="128" t="s">
+    <row r="2" spans="1:26" ht="15">
+      <c r="A2" s="136" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="135"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -8246,7 +8204,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -8274,7 +8232,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75">
       <c r="A4" s="20" t="s">
         <v>16</v>
       </c>
@@ -8332,7 +8290,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>22</v>
@@ -8383,7 +8341,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>37</v>
@@ -8431,7 +8389,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75">
       <c r="A7" s="12"/>
       <c r="B7" s="13" t="s">
         <v>36</v>
@@ -8461,7 +8419,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>38</v>
@@ -8491,7 +8449,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75">
       <c r="A9" s="12"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -8519,7 +8477,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -8547,7 +8505,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75">
       <c r="A11" s="12"/>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -8575,7 +8533,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -8603,7 +8561,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75">
       <c r="A13" s="12"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -8631,7 +8589,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -8659,7 +8617,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75">
       <c r="A15" s="12"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -8687,7 +8645,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -8715,7 +8673,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75">
       <c r="A17" s="12"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -8743,7 +8701,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -8771,7 +8729,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75">
       <c r="A19" s="12"/>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -8799,7 +8757,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -8827,7 +8785,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75">
       <c r="A21" s="12"/>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -8855,7 +8813,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -8883,7 +8841,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75">
       <c r="A23" s="12"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -8911,7 +8869,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -8939,7 +8897,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="18.75">
       <c r="A25" s="12"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -8967,7 +8925,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" thickBot="1">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -8995,7 +8953,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="18.75">
       <c r="A27" s="12"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -9023,7 +8981,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="19.5" thickBot="1">
       <c r="A28" s="16"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -9051,7 +9009,7 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" ht="18.75">
       <c r="A29" s="12"/>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -9079,7 +9037,7 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="19.5" thickBot="1">
       <c r="A30" s="16"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -9123,37 +9081,37 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4D1C59C-7F9E-CE4C-B410-088C8215B2AE}">
   <dimension ref="A1:Z10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="93" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="93" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="93" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="93" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="93" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="93" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="93" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="93" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="93" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="93" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.5" style="93" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="93" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="93"/>
+    <col min="15" max="15" width="9.42578125" style="93" customWidth="1"/>
+    <col min="16" max="26" width="8.7109375" style="93" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="93"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="17" x14ac:dyDescent="0.3">
-      <c r="A1" s="159" t="s">
+    <row r="1" spans="1:26" ht="17.25">
+      <c r="A1" s="167" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
-      <c r="K1" s="160"/>
-      <c r="L1" s="160"/>
-      <c r="M1" s="160"/>
-      <c r="N1" s="160"/>
-      <c r="O1" s="160"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="168"/>
+      <c r="H1" s="168"/>
+      <c r="I1" s="168"/>
+      <c r="J1" s="168"/>
+      <c r="K1" s="168"/>
+      <c r="L1" s="168"/>
+      <c r="M1" s="168"/>
+      <c r="N1" s="168"/>
+      <c r="O1" s="168"/>
       <c r="P1" s="94"/>
       <c r="Q1" s="94"/>
       <c r="R1" s="94"/>
@@ -9166,24 +9124,24 @@
       <c r="Y1" s="94"/>
       <c r="Z1" s="94"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="161" t="s">
+    <row r="2" spans="1:26" ht="15">
+      <c r="A2" s="169" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="160"/>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
-      <c r="K2" s="160"/>
-      <c r="L2" s="160"/>
-      <c r="M2" s="160"/>
-      <c r="N2" s="160"/>
-      <c r="O2" s="160"/>
+      <c r="B2" s="168"/>
+      <c r="C2" s="168"/>
+      <c r="D2" s="168"/>
+      <c r="E2" s="168"/>
+      <c r="F2" s="168"/>
+      <c r="G2" s="168"/>
+      <c r="H2" s="168"/>
+      <c r="I2" s="168"/>
+      <c r="J2" s="168"/>
+      <c r="K2" s="168"/>
+      <c r="L2" s="168"/>
+      <c r="M2" s="168"/>
+      <c r="N2" s="168"/>
+      <c r="O2" s="168"/>
       <c r="P2" s="94"/>
       <c r="Q2" s="94"/>
       <c r="R2" s="94"/>
@@ -9196,7 +9154,7 @@
       <c r="Y2" s="94"/>
       <c r="Z2" s="94"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1">
       <c r="A3" s="95"/>
       <c r="B3" s="94"/>
       <c r="C3" s="96"/>
@@ -9224,7 +9182,7 @@
       <c r="Y3" s="94"/>
       <c r="Z3" s="94"/>
     </row>
-    <row r="4" spans="1:26" ht="40" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="37.5">
       <c r="A4" s="98" t="s">
         <v>16</v>
       </c>
@@ -9282,7 +9240,7 @@
       <c r="Y4" s="95"/>
       <c r="Z4" s="95"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75">
       <c r="A5" s="101"/>
       <c r="B5" s="102" t="s">
         <v>22</v>
@@ -9333,7 +9291,7 @@
       <c r="Y5" s="95"/>
       <c r="Z5" s="95"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1">
       <c r="A6" s="105"/>
       <c r="B6" s="106" t="s">
         <v>37</v>
@@ -9381,7 +9339,7 @@
       <c r="Y6" s="95"/>
       <c r="Z6" s="95"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="30">
       <c r="A7" s="109" t="s">
         <v>43</v>
       </c>
@@ -9439,7 +9397,7 @@
       <c r="Y7" s="94"/>
       <c r="Z7" s="94"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="30.75" thickBot="1">
       <c r="A8" s="113"/>
       <c r="B8" s="114" t="s">
         <v>38</v>
@@ -9502,7 +9460,7 @@
       <c r="Y8" s="94"/>
       <c r="Z8" s="94"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75">
       <c r="A9" s="109" t="s">
         <v>82</v>
       </c>
@@ -9558,7 +9516,7 @@
       <c r="Y9" s="94"/>
       <c r="Z9" s="94"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1">
       <c r="A10" s="113"/>
       <c r="B10" s="114"/>
       <c r="C10" s="114">
@@ -9635,37 +9593,37 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D570C757-B716-FC4E-9C7E-AF3ECCA3BD91}">
   <dimension ref="A1:Z20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="3"/>
+    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="8.7109375" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+    <row r="1" spans="1:26" ht="26.25">
+      <c r="A1" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
+      <c r="O1" s="135"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
@@ -9678,24 +9636,24 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="128" t="s">
+    <row r="2" spans="1:26" ht="15">
+      <c r="A2" s="136" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="135"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -9708,7 +9666,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -9736,7 +9694,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75">
       <c r="A4" s="20" t="s">
         <v>16</v>
       </c>
@@ -9794,7 +9752,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>22</v>
@@ -9845,7 +9803,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>37</v>
@@ -9893,7 +9851,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75">
       <c r="A7" s="12" t="s">
         <v>43</v>
       </c>
@@ -9951,7 +9909,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>38</v>
@@ -10014,7 +9972,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75">
       <c r="A9" s="12" t="s">
         <v>25</v>
       </c>
@@ -10070,7 +10028,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -10131,7 +10089,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75">
       <c r="A11" s="12" t="s">
         <v>85</v>
       </c>
@@ -10184,7 +10142,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -10218,7 +10176,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75">
       <c r="A13" s="12" t="s">
         <v>28</v>
       </c>
@@ -10274,7 +10232,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -10335,7 +10293,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75">
       <c r="A15" s="12" t="s">
         <v>24</v>
       </c>
@@ -10391,7 +10349,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -10452,7 +10410,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75">
       <c r="A17" s="12" t="s">
         <v>76</v>
       </c>
@@ -10505,7 +10463,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -10566,7 +10524,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75">
       <c r="A19" s="12" t="s">
         <v>26</v>
       </c>
@@ -10622,7 +10580,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -10699,37 +10657,37 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EB761E0-E44A-664C-81AB-F821FA9D3978}">
   <dimension ref="A1:Z28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="3"/>
+    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="8.7109375" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+    <row r="1" spans="1:26" ht="26.25">
+      <c r="A1" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
+      <c r="O1" s="135"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
@@ -10742,24 +10700,24 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="128" t="s">
+    <row r="2" spans="1:26" ht="15">
+      <c r="A2" s="136" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="135"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -10772,7 +10730,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -10800,7 +10758,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75">
       <c r="A4" s="20" t="s">
         <v>16</v>
       </c>
@@ -10858,7 +10816,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>22</v>
@@ -10909,7 +10867,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>37</v>
@@ -10957,7 +10915,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75">
       <c r="A7" s="12" t="s">
         <v>26</v>
       </c>
@@ -11015,7 +10973,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>38</v>
@@ -11078,7 +11036,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75">
       <c r="A9" s="12" t="s">
         <v>27</v>
       </c>
@@ -11134,7 +11092,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -11195,7 +11153,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75">
       <c r="A11" s="12" t="s">
         <v>82</v>
       </c>
@@ -11248,7 +11206,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -11309,7 +11267,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75">
       <c r="A13" s="12" t="s">
         <v>43</v>
       </c>
@@ -11365,7 +11323,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -11426,7 +11384,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75">
       <c r="A15" s="12" t="s">
         <v>77</v>
       </c>
@@ -11479,7 +11437,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -11510,7 +11468,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75">
       <c r="A17" s="12" t="s">
         <v>76</v>
       </c>
@@ -11563,7 +11521,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -11624,7 +11582,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75">
       <c r="A19" s="12" t="s">
         <v>24</v>
       </c>
@@ -11680,7 +11638,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -11741,7 +11699,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75">
       <c r="A21" s="12" t="s">
         <v>23</v>
       </c>
@@ -11774,7 +11732,7 @@
         <v>4</v>
       </c>
       <c r="L21" s="14">
-        <f t="shared" ref="L21:L28" si="2">IF(SUM(C21:K21)&gt;0, SUM(C21:K21),"")</f>
+        <f t="shared" ref="L21:L27" si="2">IF(SUM(C21:K21)&gt;0, SUM(C21:K21),"")</f>
         <v>42</v>
       </c>
       <c r="M21" s="13">
@@ -11797,7 +11755,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17">
@@ -11858,7 +11816,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75">
       <c r="A23" s="12" t="s">
         <v>25</v>
       </c>
@@ -11914,7 +11872,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17">
@@ -11975,7 +11933,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="18.75">
       <c r="A25" s="12" t="s">
         <v>90</v>
       </c>
@@ -12028,7 +11986,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" thickBot="1">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -12062,7 +12020,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="18.75">
       <c r="A27" s="12" t="s">
         <v>91</v>
       </c>
@@ -12101,7 +12059,7 @@
       <c r="M27" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="N27" s="168"/>
+      <c r="N27" s="129"/>
       <c r="O27" s="15"/>
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
@@ -12115,7 +12073,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="19.5" thickBot="1">
       <c r="A28" s="16"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
